--- a/outputs/daily/hr_rankings_2026-06-28_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-06-28_full.xlsx
@@ -6706,34 +6706,30 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6990,34 +6986,30 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8394,34 +8386,30 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19856,28 +19844,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y70" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -25166,34 +25158,30 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -27130,34 +27118,30 @@
       </c>
       <c r="W96" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -31598,34 +31582,30 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -36900,28 +36880,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr"/>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y131" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB131" t="inlineStr"/>
       <c r="AC131" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -62848,28 +62832,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W224" t="inlineStr"/>
-      <c r="X224" t="inlineStr"/>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y224" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB224" t="inlineStr"/>
       <c r="AC224" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
